--- a/data/trans_orig/IP2902-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP2902-Edad-trans_orig.xlsx
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>20327</t>
+          <t>19808</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>33719</t>
+          <t>34449</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>20,53%</t>
+          <t>20,01%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>34,06%</t>
+          <t>34,79%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>23911</t>
+          <t>23468</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>39310</t>
+          <t>38673</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>21,81%</t>
+          <t>21,41%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>35,85%</t>
+          <t>35,27%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>47044</t>
+          <t>47409</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>67470</t>
+          <t>67014</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>22,55%</t>
+          <t>22,72%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>32,34%</t>
+          <t>32,12%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4486</t>
+          <t>4481</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>13436</t>
+          <t>13677</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>13,57%</t>
+          <t>13,81%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>7258</t>
+          <t>6820</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>17294</t>
+          <t>17666</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>6,22%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>15,77%</t>
+          <t>16,11%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>13656</t>
+          <t>14382</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>26951</t>
+          <t>27236</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>6,54%</t>
+          <t>6,89%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>12,92%</t>
+          <t>13,05%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>56521</t>
+          <t>55965</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>71222</t>
+          <t>71482</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>57,09%</t>
+          <t>56,52%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>71,93%</t>
+          <t>72,2%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>59260</t>
+          <t>59036</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>75229</t>
+          <t>75691</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>54,05%</t>
+          <t>53,85%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>68,62%</t>
+          <t>69,04%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>121097</t>
+          <t>121271</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>143231</t>
+          <t>142852</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>58,04%</t>
+          <t>58,12%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>68,65%</t>
+          <t>68,47%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>46978</t>
+          <t>47465</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>69124</t>
+          <t>69626</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>18,82%</t>
+          <t>19,02%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>27,69%</t>
+          <t>27,89%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>53344</t>
+          <t>53818</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>75762</t>
+          <t>76173</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>21,32%</t>
+          <t>21,51%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>30,28%</t>
+          <t>30,44%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>106614</t>
+          <t>106885</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>138183</t>
+          <t>138082</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>21,33%</t>
+          <t>21,38%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>27,64%</t>
+          <t>27,62%</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>30711</t>
+          <t>30727</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>48768</t>
+          <t>50001</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1316,12 +1316,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>12,3%</t>
+          <t>12,31%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>19,54%</t>
+          <t>20,03%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1336,12 +1336,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>29826</t>
+          <t>30566</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>48773</t>
+          <t>49305</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1351,12 +1351,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>11,92%</t>
+          <t>12,21%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>19,49%</t>
+          <t>19,7%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1371,12 +1371,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>66165</t>
+          <t>65756</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>91161</t>
+          <t>90636</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1386,12 +1386,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>13,24%</t>
+          <t>13,15%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>18,24%</t>
+          <t>18,13%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>139235</t>
+          <t>139182</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>163817</t>
+          <t>164725</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>55,78%</t>
+          <t>55,76%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>65,63%</t>
+          <t>65,99%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>134217</t>
+          <t>133720</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>160936</t>
+          <t>159576</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>53,64%</t>
+          <t>53,44%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>64,31%</t>
+          <t>63,77%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>280273</t>
+          <t>281852</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>318210</t>
+          <t>317835</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>56,07%</t>
+          <t>56,39%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>63,66%</t>
+          <t>63,58%</t>
         </is>
       </c>
     </row>
@@ -1644,12 +1644,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>24428</t>
+          <t>23936</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>39963</t>
+          <t>39526</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1659,12 +1659,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>19,71%</t>
+          <t>19,32%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>32,25%</t>
+          <t>31,9%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1679,12 +1679,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>28840</t>
+          <t>28823</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>44815</t>
+          <t>46315</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1694,12 +1694,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>21,09%</t>
+          <t>21,08%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>32,78%</t>
+          <t>33,87%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1714,12 +1714,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>56805</t>
+          <t>56311</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>80178</t>
+          <t>79594</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1729,12 +1729,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>21,79%</t>
+          <t>21,6%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>30,76%</t>
+          <t>30,54%</t>
         </is>
       </c>
     </row>
@@ -1757,12 +1757,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>8923</t>
+          <t>8974</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>20217</t>
+          <t>20771</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1772,12 +1772,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>7,24%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>16,31%</t>
+          <t>16,76%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1792,12 +1792,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>12808</t>
+          <t>12918</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>26479</t>
+          <t>26865</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1807,12 +1807,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>9,37%</t>
+          <t>9,45%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>19,37%</t>
+          <t>19,65%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1827,12 +1827,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>24862</t>
+          <t>25682</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>42805</t>
+          <t>42919</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1842,12 +1842,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>9,54%</t>
+          <t>9,85%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>16,42%</t>
+          <t>16,47%</t>
         </is>
       </c>
     </row>
@@ -1870,12 +1870,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>68988</t>
+          <t>69635</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>86766</t>
+          <t>87635</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1885,12 +1885,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>55,67%</t>
+          <t>56,19%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>70,02%</t>
+          <t>70,72%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1905,12 +1905,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>71478</t>
+          <t>71820</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>89642</t>
+          <t>89944</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1920,12 +1920,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>52,28%</t>
+          <t>52,53%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>65,56%</t>
+          <t>65,78%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1940,12 +1940,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>146131</t>
+          <t>146702</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>171447</t>
+          <t>172231</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1955,12 +1955,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>56,06%</t>
+          <t>56,28%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>65,77%</t>
+          <t>66,08%</t>
         </is>
       </c>
     </row>
@@ -2100,12 +2100,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>36046</t>
+          <t>34809</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>54958</t>
+          <t>54480</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2115,12 +2115,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>19,13%</t>
+          <t>18,47%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>29,16%</t>
+          <t>28,91%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2135,12 +2135,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>34577</t>
+          <t>34821</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>53157</t>
+          <t>53817</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2150,12 +2150,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>17,06%</t>
+          <t>17,18%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>26,23%</t>
+          <t>26,55%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2170,12 +2170,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>75660</t>
+          <t>76109</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>102350</t>
+          <t>102978</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2185,12 +2185,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>19,34%</t>
+          <t>19,46%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>26,17%</t>
+          <t>26,33%</t>
         </is>
       </c>
     </row>
@@ -2213,12 +2213,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>10798</t>
+          <t>10800</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>23530</t>
+          <t>23130</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,7 +2233,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>12,49%</t>
+          <t>12,27%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2248,12 +2248,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>16569</t>
+          <t>15404</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>30436</t>
+          <t>31376</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2263,12 +2263,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>8,17%</t>
+          <t>7,6%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>15,02%</t>
+          <t>15,48%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>30700</t>
+          <t>29977</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>50188</t>
+          <t>50189</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2298,7 +2298,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>7,85%</t>
+          <t>7,66%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2326,12 +2326,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>116534</t>
+          <t>116315</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>136839</t>
+          <t>136867</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2341,12 +2341,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>61,84%</t>
+          <t>61,73%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>72,62%</t>
+          <t>72,63%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2361,12 +2361,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>125666</t>
+          <t>124048</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>146835</t>
+          <t>146799</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2376,12 +2376,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>62,0%</t>
+          <t>61,2%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>72,45%</t>
+          <t>72,43%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2396,12 +2396,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>249093</t>
+          <t>248610</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>277457</t>
+          <t>279059</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2411,12 +2411,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>63,69%</t>
+          <t>63,56%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>70,94%</t>
+          <t>71,35%</t>
         </is>
       </c>
     </row>
@@ -2556,12 +2556,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>141074</t>
+          <t>142679</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>177498</t>
+          <t>177534</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2571,12 +2571,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>21,34%</t>
+          <t>21,59%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>26,85%</t>
+          <t>26,86%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2591,12 +2591,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>157117</t>
+          <t>158721</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>193258</t>
+          <t>195439</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2606,12 +2606,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>22,47%</t>
+          <t>22,7%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>27,64%</t>
+          <t>27,95%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2626,12 +2626,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>310916</t>
+          <t>312500</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>361299</t>
+          <t>360328</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2641,12 +2641,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>22,86%</t>
+          <t>22,97%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>26,56%</t>
+          <t>26,49%</t>
         </is>
       </c>
     </row>
@@ -2669,12 +2669,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>66662</t>
+          <t>66446</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>90879</t>
+          <t>93239</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2684,12 +2684,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>10,08%</t>
+          <t>10,05%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>13,75%</t>
+          <t>14,11%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2704,12 +2704,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>78337</t>
+          <t>78878</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>106384</t>
+          <t>106461</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2719,12 +2719,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>11,2%</t>
+          <t>11,28%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>15,21%</t>
+          <t>15,22%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2739,12 +2739,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>150722</t>
+          <t>151377</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>189952</t>
+          <t>190237</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2754,12 +2754,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>11,08%</t>
+          <t>11,13%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>13,96%</t>
+          <t>13,98%</t>
         </is>
       </c>
     </row>
@@ -2782,12 +2782,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>401969</t>
+          <t>403199</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>442491</t>
+          <t>440745</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2797,12 +2797,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>60,81%</t>
+          <t>61,0%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>66,94%</t>
+          <t>66,68%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2817,12 +2817,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>410571</t>
+          <t>411008</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>451712</t>
+          <t>452874</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2832,12 +2832,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>58,71%</t>
+          <t>58,77%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>64,6%</t>
+          <t>64,76%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2852,12 +2852,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>826628</t>
+          <t>824815</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>884332</t>
+          <t>881227</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2867,12 +2867,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>60,77%</t>
+          <t>60,64%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>65,01%</t>
+          <t>64,78%</t>
         </is>
       </c>
     </row>
@@ -3244,12 +3244,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>36215</t>
+          <t>35936</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>53619</t>
+          <t>53370</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3259,12 +3259,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>25,43%</t>
+          <t>25,24%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>37,66%</t>
+          <t>37,48%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3279,12 +3279,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>34139</t>
+          <t>33240</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>50874</t>
+          <t>51045</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3294,12 +3294,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>23,91%</t>
+          <t>23,28%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>35,63%</t>
+          <t>35,75%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>74145</t>
+          <t>74430</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>98496</t>
+          <t>98171</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3329,12 +3329,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>26,0%</t>
+          <t>26,1%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>34,54%</t>
+          <t>34,43%</t>
         </is>
       </c>
     </row>
@@ -3357,12 +3357,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>13179</t>
+          <t>12844</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>26463</t>
+          <t>26018</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3372,12 +3372,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>9,26%</t>
+          <t>9,02%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>18,58%</t>
+          <t>18,27%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3392,12 +3392,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>18411</t>
+          <t>18368</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>33813</t>
+          <t>33419</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3407,12 +3407,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>12,9%</t>
+          <t>12,87%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>23,68%</t>
+          <t>23,41%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3427,12 +3427,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>35625</t>
+          <t>34910</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>54935</t>
+          <t>55136</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3442,12 +3442,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>12,49%</t>
+          <t>12,24%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>19,26%</t>
+          <t>19,34%</t>
         </is>
       </c>
     </row>
@@ -3470,12 +3470,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>69292</t>
+          <t>69654</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>87612</t>
+          <t>89232</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3485,12 +3485,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>48,66%</t>
+          <t>48,92%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>61,53%</t>
+          <t>62,67%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3505,12 +3505,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>66239</t>
+          <t>65388</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>85755</t>
+          <t>84515</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3520,12 +3520,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>46,4%</t>
+          <t>45,8%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>60,07%</t>
+          <t>59,2%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3540,12 +3540,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>142100</t>
+          <t>140442</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>168379</t>
+          <t>167976</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>49,83%</t>
+          <t>49,25%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>59,05%</t>
+          <t>58,91%</t>
         </is>
       </c>
     </row>
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>53052</t>
+          <t>54368</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>76013</t>
+          <t>76135</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3715,12 +3715,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>22,58%</t>
+          <t>23,14%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>32,35%</t>
+          <t>32,4%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3735,12 +3735,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>73835</t>
+          <t>72939</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>99437</t>
+          <t>98942</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3750,12 +3750,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>27,87%</t>
+          <t>27,53%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>37,54%</t>
+          <t>37,35%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3770,12 +3770,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>132725</t>
+          <t>133831</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>167235</t>
+          <t>168574</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3785,12 +3785,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>26,55%</t>
+          <t>26,77%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>33,45%</t>
+          <t>33,72%</t>
         </is>
       </c>
     </row>
@@ -3813,12 +3813,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>19004</t>
+          <t>18616</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>35169</t>
+          <t>34099</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -3828,12 +3828,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>8,09%</t>
+          <t>7,92%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>14,97%</t>
+          <t>14,51%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -3848,12 +3848,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>21953</t>
+          <t>22234</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>38946</t>
+          <t>38988</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>8,29%</t>
+          <t>8,39%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>14,7%</t>
+          <t>14,72%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -3883,12 +3883,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>45303</t>
+          <t>45588</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>68242</t>
+          <t>67488</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3898,12 +3898,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>9,06%</t>
+          <t>9,12%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>13,65%</t>
+          <t>13,5%</t>
         </is>
       </c>
     </row>
@@ -3926,12 +3926,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>130728</t>
+          <t>132379</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>156295</t>
+          <t>156794</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3941,12 +3941,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>55,63%</t>
+          <t>56,33%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>66,51%</t>
+          <t>66,72%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3961,12 +3961,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>136520</t>
+          <t>135190</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>163483</t>
+          <t>162558</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3976,12 +3976,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>51,53%</t>
+          <t>51,03%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>61,71%</t>
+          <t>61,36%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3996,12 +3996,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>276524</t>
+          <t>274573</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>313338</t>
+          <t>310913</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4011,12 +4011,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>55,32%</t>
+          <t>54,92%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>62,68%</t>
+          <t>62,19%</t>
         </is>
       </c>
     </row>
@@ -4156,12 +4156,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>37594</t>
+          <t>37742</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>57836</t>
+          <t>56868</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4171,12 +4171,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>23,94%</t>
+          <t>24,03%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>36,83%</t>
+          <t>36,21%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>39360</t>
+          <t>39840</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>59114</t>
+          <t>58417</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4206,12 +4206,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>25,41%</t>
+          <t>25,72%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>38,17%</t>
+          <t>37,72%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4226,12 +4226,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>83728</t>
+          <t>84065</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>110644</t>
+          <t>109660</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4241,12 +4241,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>26,84%</t>
+          <t>26,95%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>35,47%</t>
+          <t>35,16%</t>
         </is>
       </c>
     </row>
@@ -4269,12 +4269,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>10758</t>
+          <t>10446</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>23601</t>
+          <t>23152</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4284,12 +4284,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,85%</t>
+          <t>6,65%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>15,03%</t>
+          <t>14,74%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4304,12 +4304,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>15417</t>
+          <t>15540</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>29995</t>
+          <t>29719</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4319,12 +4319,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>9,95%</t>
+          <t>10,03%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>19,37%</t>
+          <t>19,19%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4339,12 +4339,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>30422</t>
+          <t>29544</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>49717</t>
+          <t>48228</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4354,12 +4354,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>9,75%</t>
+          <t>9,47%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>15,94%</t>
+          <t>15,46%</t>
         </is>
       </c>
     </row>
@@ -4382,12 +4382,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>82824</t>
+          <t>83920</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>104907</t>
+          <t>103466</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4397,12 +4397,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>52,74%</t>
+          <t>53,44%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>66,8%</t>
+          <t>65,88%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4417,12 +4417,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>72921</t>
+          <t>73336</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>94447</t>
+          <t>94418</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>47,08%</t>
+          <t>47,35%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>60,98%</t>
+          <t>60,96%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4452,12 +4452,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>162858</t>
+          <t>162867</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>192533</t>
+          <t>190946</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4472,7 +4472,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>61,72%</t>
+          <t>61,21%</t>
         </is>
       </c>
     </row>
@@ -4612,12 +4612,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>36525</t>
+          <t>36424</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>55281</t>
+          <t>55495</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4627,12 +4627,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>21,75%</t>
+          <t>21,69%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>32,92%</t>
+          <t>33,05%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4647,12 +4647,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>47518</t>
+          <t>48102</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>68321</t>
+          <t>68364</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>26,91%</t>
+          <t>27,24%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>38,69%</t>
+          <t>38,71%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4682,12 +4682,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>90051</t>
+          <t>89717</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>118529</t>
+          <t>118299</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>26,14%</t>
+          <t>26,04%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>34,4%</t>
+          <t>34,34%</t>
         </is>
       </c>
     </row>
@@ -4725,12 +4725,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>12835</t>
+          <t>13380</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>27543</t>
+          <t>26596</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4740,12 +4740,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>7,64%</t>
+          <t>7,97%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>16,4%</t>
+          <t>15,84%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4760,12 +4760,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>9488</t>
+          <t>9241</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>21666</t>
+          <t>21488</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>12,27%</t>
+          <t>12,17%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4795,12 +4795,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>25286</t>
+          <t>26477</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>43705</t>
+          <t>44154</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>7,34%</t>
+          <t>7,69%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>12,69%</t>
+          <t>12,82%</t>
         </is>
       </c>
     </row>
@@ -4838,12 +4838,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>92926</t>
+          <t>93091</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>113828</t>
+          <t>113713</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -4853,12 +4853,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>55,34%</t>
+          <t>55,43%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>67,78%</t>
+          <t>67,71%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -4873,12 +4873,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>93709</t>
+          <t>93457</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>115063</t>
+          <t>115069</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4888,7 +4888,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>53,07%</t>
+          <t>52,92%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -4908,12 +4908,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>192764</t>
+          <t>193643</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>222531</t>
+          <t>224043</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>55,95%</t>
+          <t>56,21%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>64,59%</t>
+          <t>65,03%</t>
         </is>
       </c>
     </row>
@@ -5068,12 +5068,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>182270</t>
+          <t>183510</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>219449</t>
+          <t>222753</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5083,12 +5083,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>25,95%</t>
+          <t>26,13%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>31,24%</t>
+          <t>31,72%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5103,12 +5103,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>212118</t>
+          <t>214237</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>254953</t>
+          <t>253551</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>28,7%</t>
+          <t>28,98%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>34,49%</t>
+          <t>34,3%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5138,12 +5138,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>407196</t>
+          <t>409343</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>463469</t>
+          <t>464516</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>28,25%</t>
+          <t>28,4%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>32,15%</t>
+          <t>32,22%</t>
         </is>
       </c>
     </row>
@@ -5181,12 +5181,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>66985</t>
+          <t>68087</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>94218</t>
+          <t>95181</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -5196,12 +5196,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>9,54%</t>
+          <t>9,69%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>13,41%</t>
+          <t>13,55%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -5216,12 +5216,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>77089</t>
+          <t>78072</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>107160</t>
+          <t>106403</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>10,43%</t>
+          <t>10,56%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>14,5%</t>
+          <t>14,4%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -5251,12 +5251,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>152899</t>
+          <t>155473</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>193067</t>
+          <t>194805</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>10,61%</t>
+          <t>10,79%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>13,39%</t>
+          <t>13,51%</t>
         </is>
       </c>
     </row>
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>398306</t>
+          <t>398049</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>440979</t>
+          <t>441660</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5309,12 +5309,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>56,71%</t>
+          <t>56,67%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>62,79%</t>
+          <t>62,88%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5329,12 +5329,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>391947</t>
+          <t>393101</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>439168</t>
+          <t>436109</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5344,12 +5344,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>53,03%</t>
+          <t>53,18%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>59,42%</t>
+          <t>59,0%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5364,12 +5364,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>802360</t>
+          <t>802786</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>861957</t>
+          <t>865015</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5379,12 +5379,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>55,66%</t>
+          <t>55,69%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>59,8%</t>
+          <t>60,01%</t>
         </is>
       </c>
     </row>
@@ -5756,12 +5756,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>11976</t>
+          <t>11844</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>23964</t>
+          <t>23544</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5771,12 +5771,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>9,37%</t>
+          <t>9,26%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>18,74%</t>
+          <t>18,42%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5791,12 +5791,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>19227</t>
+          <t>19570</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>33798</t>
+          <t>33817</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>16,2%</t>
+          <t>16,49%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>28,47%</t>
+          <t>28,49%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5826,12 +5826,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>34232</t>
+          <t>34346</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>54183</t>
+          <t>54477</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5841,12 +5841,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>13,88%</t>
+          <t>13,93%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>21,98%</t>
+          <t>22,1%</t>
         </is>
       </c>
     </row>
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>12552</t>
+          <t>12615</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>25180</t>
+          <t>25198</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5884,12 +5884,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>9,82%</t>
+          <t>9,87%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>19,7%</t>
+          <t>19,71%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5904,12 +5904,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>17560</t>
+          <t>17415</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>31533</t>
+          <t>32233</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5919,12 +5919,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>14,79%</t>
+          <t>14,67%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>26,56%</t>
+          <t>27,15%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5939,12 +5939,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>34074</t>
+          <t>34201</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>52771</t>
+          <t>52643</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5954,12 +5954,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>13,82%</t>
+          <t>13,87%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>21,4%</t>
+          <t>21,35%</t>
         </is>
       </c>
     </row>
@@ -5982,12 +5982,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>83994</t>
+          <t>83788</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>99978</t>
+          <t>99835</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5997,12 +5997,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>65,7%</t>
+          <t>65,54%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>78,2%</t>
+          <t>78,09%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6017,12 +6017,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>60157</t>
+          <t>59584</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>76315</t>
+          <t>77330</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6032,12 +6032,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>50,68%</t>
+          <t>50,19%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>64,29%</t>
+          <t>65,14%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6052,12 +6052,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>147883</t>
+          <t>149046</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>172010</t>
+          <t>172830</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6067,12 +6067,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>59,98%</t>
+          <t>60,45%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>69,76%</t>
+          <t>70,1%</t>
         </is>
       </c>
     </row>
@@ -6212,12 +6212,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>28018</t>
+          <t>27917</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>45871</t>
+          <t>45208</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6227,12 +6227,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>13,42%</t>
+          <t>13,37%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>21,98%</t>
+          <t>21,66%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6247,12 +6247,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>33722</t>
+          <t>33380</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>51901</t>
+          <t>51542</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>13,24%</t>
+          <t>13,1%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>20,38%</t>
+          <t>20,24%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6282,12 +6282,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>66610</t>
+          <t>65567</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>92498</t>
+          <t>91473</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>14,37%</t>
+          <t>14,15%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>19,96%</t>
+          <t>19,74%</t>
         </is>
       </c>
     </row>
@@ -6325,12 +6325,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>24504</t>
+          <t>24316</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>40716</t>
+          <t>40517</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6340,12 +6340,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>11,74%</t>
+          <t>11,65%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>19,51%</t>
+          <t>19,41%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -6360,12 +6360,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>34577</t>
+          <t>34836</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>53223</t>
+          <t>54189</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6375,12 +6375,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>13,58%</t>
+          <t>13,68%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>20,9%</t>
+          <t>21,27%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -6395,12 +6395,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>62517</t>
+          <t>62148</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>87899</t>
+          <t>87271</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6410,12 +6410,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>13,49%</t>
+          <t>13,41%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>18,97%</t>
+          <t>18,83%</t>
         </is>
       </c>
     </row>
@@ -6438,12 +6438,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>129180</t>
+          <t>130572</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>151195</t>
+          <t>150727</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6453,12 +6453,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>61,89%</t>
+          <t>62,55%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>72,43%</t>
+          <t>72,21%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6473,12 +6473,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>156063</t>
+          <t>156494</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>180415</t>
+          <t>181837</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6488,12 +6488,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>61,27%</t>
+          <t>61,44%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>70,83%</t>
+          <t>71,39%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6508,12 +6508,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>293071</t>
+          <t>295938</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>325512</t>
+          <t>326384</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6523,12 +6523,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>63,24%</t>
+          <t>63,86%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>70,24%</t>
+          <t>70,43%</t>
         </is>
       </c>
     </row>
@@ -6668,12 +6668,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>30145</t>
+          <t>30516</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>47989</t>
+          <t>48035</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6683,12 +6683,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>16,11%</t>
+          <t>16,31%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>25,64%</t>
+          <t>25,67%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6703,12 +6703,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>27476</t>
+          <t>26822</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>44905</t>
+          <t>45440</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6718,12 +6718,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>14,84%</t>
+          <t>14,49%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>24,26%</t>
+          <t>24,55%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6738,12 +6738,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>61069</t>
+          <t>62714</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>87425</t>
+          <t>88571</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6753,12 +6753,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>16,4%</t>
+          <t>16,85%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>23,48%</t>
+          <t>23,79%</t>
         </is>
       </c>
     </row>
@@ -6781,12 +6781,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>29368</t>
+          <t>29382</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>47431</t>
+          <t>47327</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6796,12 +6796,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>15,69%</t>
+          <t>15,7%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>25,34%</t>
+          <t>25,29%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6816,12 +6816,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>14621</t>
+          <t>15525</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>29867</t>
+          <t>29468</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6831,12 +6831,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>8,39%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>16,13%</t>
+          <t>15,92%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6851,12 +6851,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>48345</t>
+          <t>47496</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>72006</t>
+          <t>70468</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6866,12 +6866,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>12,99%</t>
+          <t>12,76%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>19,34%</t>
+          <t>18,93%</t>
         </is>
       </c>
     </row>
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>98914</t>
+          <t>100051</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>121431</t>
+          <t>120757</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6909,12 +6909,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>52,85%</t>
+          <t>53,46%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>64,88%</t>
+          <t>64,52%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6929,12 +6929,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>117756</t>
+          <t>116538</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>138943</t>
+          <t>138452</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6944,12 +6944,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>63,61%</t>
+          <t>62,95%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>75,06%</t>
+          <t>74,79%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6964,12 +6964,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>223182</t>
+          <t>223814</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>253561</t>
+          <t>254546</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6979,12 +6979,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>59,95%</t>
+          <t>60,12%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>68,11%</t>
+          <t>68,38%</t>
         </is>
       </c>
     </row>
@@ -7124,12 +7124,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>37317</t>
+          <t>37114</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>56800</t>
+          <t>56720</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7139,12 +7139,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>22,56%</t>
+          <t>22,44%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>34,34%</t>
+          <t>34,29%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7159,12 +7159,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>26622</t>
+          <t>26925</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>43719</t>
+          <t>44009</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7174,12 +7174,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>16,08%</t>
+          <t>16,26%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>26,41%</t>
+          <t>26,58%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7194,12 +7194,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>67853</t>
+          <t>67153</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>94389</t>
+          <t>93968</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7209,12 +7209,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>20,5%</t>
+          <t>20,29%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>28,52%</t>
+          <t>28,39%</t>
         </is>
       </c>
     </row>
@@ -7237,12 +7237,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>13987</t>
+          <t>13566</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>28548</t>
+          <t>27745</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7252,12 +7252,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>8,46%</t>
+          <t>8,2%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>17,26%</t>
+          <t>16,78%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7272,12 +7272,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>19813</t>
+          <t>20119</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>36103</t>
+          <t>35741</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7287,12 +7287,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>11,97%</t>
+          <t>12,15%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>21,81%</t>
+          <t>21,59%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7307,12 +7307,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>37376</t>
+          <t>37054</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>58842</t>
+          <t>58494</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7322,12 +7322,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>11,29%</t>
+          <t>11,2%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>17,78%</t>
+          <t>17,67%</t>
         </is>
       </c>
     </row>
@@ -7350,12 +7350,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>88920</t>
+          <t>87740</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>109906</t>
+          <t>108942</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -7365,12 +7365,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>53,76%</t>
+          <t>53,05%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>66,45%</t>
+          <t>65,87%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -7385,12 +7385,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>93056</t>
+          <t>92867</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>113946</t>
+          <t>113231</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -7400,12 +7400,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>56,21%</t>
+          <t>56,1%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>68,83%</t>
+          <t>68,4%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -7420,12 +7420,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>187666</t>
+          <t>188708</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>216742</t>
+          <t>217946</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -7435,12 +7435,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>56,71%</t>
+          <t>57,02%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>65,49%</t>
+          <t>65,86%</t>
         </is>
       </c>
     </row>
@@ -7580,12 +7580,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>121796</t>
+          <t>121123</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>156203</t>
+          <t>155373</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7595,12 +7595,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>17,67%</t>
+          <t>17,58%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>22,67%</t>
+          <t>22,55%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7615,12 +7615,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>121927</t>
+          <t>121841</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>157045</t>
+          <t>155888</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7630,12 +7630,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>16,84%</t>
+          <t>16,83%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>21,69%</t>
+          <t>21,53%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7650,12 +7650,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>253969</t>
+          <t>254897</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>299064</t>
+          <t>300948</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7665,12 +7665,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>17,97%</t>
+          <t>18,04%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>21,16%</t>
+          <t>21,3%</t>
         </is>
       </c>
     </row>
@@ -7693,12 +7693,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>92911</t>
+          <t>92687</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>123823</t>
+          <t>124248</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -7708,12 +7708,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>13,48%</t>
+          <t>13,45%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>17,97%</t>
+          <t>18,03%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -7728,12 +7728,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>101670</t>
+          <t>99988</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>132128</t>
+          <t>132961</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -7743,12 +7743,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>14,04%</t>
+          <t>13,81%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>18,25%</t>
+          <t>18,36%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -7763,12 +7763,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>200036</t>
+          <t>202845</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>246839</t>
+          <t>244968</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -7778,12 +7778,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>14,15%</t>
+          <t>14,35%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>17,47%</t>
+          <t>17,33%</t>
         </is>
       </c>
     </row>
@@ -7806,12 +7806,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>422892</t>
+          <t>423121</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>463413</t>
+          <t>463199</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7821,12 +7821,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>61,37%</t>
+          <t>61,4%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>67,25%</t>
+          <t>67,21%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7841,12 +7841,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>447788</t>
+          <t>451236</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>490310</t>
+          <t>490771</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7856,12 +7856,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>61,84%</t>
+          <t>62,32%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>67,71%</t>
+          <t>67,78%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7876,12 +7876,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>883189</t>
+          <t>886026</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>940397</t>
+          <t>944300</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7891,12 +7891,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>62,49%</t>
+          <t>62,7%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>66,54%</t>
+          <t>66,82%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP2902-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP2902-Edad-trans_orig.xlsx
@@ -543,7 +543,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -554,7 +554,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -722,72 +722,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>30476</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>22756</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>38106</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>27,8%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>20,76%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>34,76%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>41</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>26310</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>19808</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>34449</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>19803</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>33963</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>26,57%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>20,01%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>34,79%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>30476</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>23468</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>38673</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>27,8%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>21,41%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>35,27%</t>
+          <t>34,3%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>47409</t>
+          <t>47291</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>67014</t>
+          <t>67751</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>22,72%</t>
+          <t>22,67%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>32,12%</t>
+          <t>32,47%</t>
         </is>
       </c>
     </row>
@@ -835,72 +835,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>11143</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>6945</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>17529</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>10,16%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>6,33%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>15,99%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>8352</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>4481</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>13677</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>4334</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>12893</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>8,44%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>4,53%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>13,81%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>11143</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>6820</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>17666</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>10,16%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>16,11%</t>
+          <t>13,02%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>14382</t>
+          <t>13699</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>27236</t>
+          <t>26538</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>6,57%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>13,05%</t>
+          <t>12,72%</t>
         </is>
       </c>
     </row>
@@ -948,72 +948,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>103</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>68017</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>60162</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>76390</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>62,04%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>54,87%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>69,68%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>97</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>64349</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>55965</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>71482</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>56116</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>71120</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>64,99%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>56,52%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>72,2%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>103</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>68017</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>59036</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>75691</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>62,04%</t>
-        </is>
-      </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>53,85%</t>
+          <t>56,68%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>69,04%</t>
+          <t>71,83%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>121271</t>
+          <t>121191</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>142852</t>
+          <t>142896</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>58,12%</t>
+          <t>58,08%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>68,47%</t>
+          <t>68,49%</t>
         </is>
       </c>
     </row>
@@ -1061,57 +1061,57 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>165</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>109636</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>109636</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>109636</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>151</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>99011</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>99011</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
         <is>
           <t>99011</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>165</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>109636</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>109636</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>109636</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1178,72 +1178,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>64826</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>53932</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>77137</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>25,91%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>21,55%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>30,82%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>85</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>57465</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>47465</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>69626</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>48080</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>68884</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>23,02%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>19,02%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>27,89%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>98</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>64826</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>53818</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>76173</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>25,91%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>21,51%</t>
+          <t>19,26%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>30,44%</t>
+          <t>27,6%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>106885</t>
+          <t>107401</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>138082</t>
+          <t>137585</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>21,38%</t>
+          <t>21,49%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>27,62%</t>
+          <t>27,52%</t>
         </is>
       </c>
     </row>
@@ -1291,72 +1291,72 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>38667</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>29925</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>48352</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>15,45%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>11,96%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>19,32%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>60</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>39609</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>30727</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>50001</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>31842</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>49537</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
         <is>
           <t>15,87%</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>12,31%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>20,03%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>57</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>38667</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>30566</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>49305</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>15,45%</t>
-        </is>
-      </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>12,21%</t>
+          <t>12,76%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>19,7%</t>
+          <t>19,85%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1371,12 +1371,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>65756</t>
+          <t>66312</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>90636</t>
+          <t>91306</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1386,12 +1386,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>13,15%</t>
+          <t>13,27%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>18,13%</t>
+          <t>18,27%</t>
         </is>
       </c>
     </row>
@@ -1404,72 +1404,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>222</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>146749</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>133246</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>158623</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>58,64%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>53,25%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>63,39%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>229</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>152545</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>139182</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>164725</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>140123</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>164596</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>61,11%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>55,76%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>65,99%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>222</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>146749</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>133720</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>159576</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>58,64%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>53,44%</t>
+          <t>56,13%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>63,77%</t>
+          <t>65,94%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>281852</t>
+          <t>280078</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>317835</t>
+          <t>315826</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>56,39%</t>
+          <t>56,03%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>63,58%</t>
+          <t>63,18%</t>
         </is>
       </c>
     </row>
@@ -1517,57 +1517,57 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>377</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>250241</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>250241</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>250241</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>374</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>249620</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
         <is>
           <t>249620</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>249620</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>377</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>250241</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>250241</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>250241</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1634,72 +1634,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>36297</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>28421</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>44847</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>26,55%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>20,79%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>32,8%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>48</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>31556</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>23936</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>39526</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>24112</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>39277</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>25,46%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>19,32%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>31,9%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>36297</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>28823</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>46315</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>26,55%</t>
-        </is>
-      </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>21,08%</t>
+          <t>19,46%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>33,87%</t>
+          <t>31,69%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1714,12 +1714,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>56311</t>
+          <t>57369</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>79594</t>
+          <t>80039</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1729,12 +1729,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>21,6%</t>
+          <t>22,01%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>30,54%</t>
+          <t>30,71%</t>
         </is>
       </c>
     </row>
@@ -1747,107 +1747,107 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>19366</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>13540</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>26506</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>14,16%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>9,9%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>19,38%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>21</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>13993</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>8974</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>20771</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>9222</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>21063</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>11,29%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>7,24%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>7,44%</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>17,0%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>33359</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>25784</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>43691</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>12,8%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>9,89%</t>
+        </is>
+      </c>
+      <c r="W13" s="2" t="inlineStr">
         <is>
           <t>16,76%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>19366</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>12918</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>26865</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>14,16%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>9,45%</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>19,65%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>49</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>33359</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>25682</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>42919</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>12,8%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>9,85%</t>
-        </is>
-      </c>
-      <c r="W13" s="2" t="inlineStr">
-        <is>
-          <t>16,47%</t>
         </is>
       </c>
     </row>
@@ -1860,72 +1860,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>122</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>81071</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>72159</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>90054</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>59,29%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>52,77%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>65,86%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>117</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>78376</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>69635</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>87635</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>68958</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>86780</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>63,24%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>56,19%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>70,72%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>122</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>81071</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>71820</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>89944</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>59,29%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>52,53%</t>
+          <t>55,64%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>65,78%</t>
+          <t>70,03%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1940,12 +1940,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>146702</t>
+          <t>146772</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>172231</t>
+          <t>171626</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1955,12 +1955,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>56,28%</t>
+          <t>56,31%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>66,08%</t>
+          <t>65,84%</t>
         </is>
       </c>
     </row>
@@ -1973,57 +1973,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>205</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>136734</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>136734</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>136734</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>186</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>123925</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>123925</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>123925</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>205</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>136734</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>136734</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>136734</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2090,72 +2090,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>43411</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>34611</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>52730</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>21,42%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>17,08%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>26,02%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>67</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>44860</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>34809</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>54480</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>35925</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>54755</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>23,81%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>18,47%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>28,91%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>66</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>43411</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>34821</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>53817</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>21,42%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>17,18%</t>
+          <t>19,06%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>26,55%</t>
+          <t>29,06%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2170,12 +2170,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>76109</t>
+          <t>74973</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>102978</t>
+          <t>101513</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2185,12 +2185,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>19,46%</t>
+          <t>19,17%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>26,33%</t>
+          <t>25,95%</t>
         </is>
       </c>
     </row>
@@ -2203,72 +2203,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>22959</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>16559</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>31356</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>11,33%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>8,17%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>15,47%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>25</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>16363</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>10800</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>23130</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>10950</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>23304</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>8,68%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>5,73%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>12,27%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>22959</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>15404</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>31376</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>11,33%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>5,81%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>15,48%</t>
+          <t>12,37%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>29977</t>
+          <t>31169</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>50189</t>
+          <t>48785</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2298,12 +2298,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>7,97%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>12,83%</t>
+          <t>12,47%</t>
         </is>
       </c>
     </row>
@@ -2316,72 +2316,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>205</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>136314</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>125650</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>146356</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>67,25%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>61,99%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>72,21%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>186</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>127218</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>116315</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>136867</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>116365</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>136947</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>67,51%</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>61,73%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>72,63%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>205</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>136314</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>124048</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>146799</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>67,25%</t>
-        </is>
-      </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>61,2%</t>
+          <t>61,75%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>72,43%</t>
+          <t>72,67%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2396,12 +2396,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>248610</t>
+          <t>247143</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>279059</t>
+          <t>277371</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2411,12 +2411,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>63,56%</t>
+          <t>63,19%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>71,35%</t>
+          <t>70,92%</t>
         </is>
       </c>
     </row>
@@ -2429,57 +2429,57 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>305</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>202684</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>202684</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>202684</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>278</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>188441</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
         <is>
           <t>188441</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="M19" s="2" t="inlineStr">
         <is>
           <t>188441</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>305</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>202684</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>202684</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>202684</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2546,72 +2546,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>264</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>175009</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>155884</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>191660</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>25,03%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>22,29%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>27,41%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>241</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>160191</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>142679</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>177534</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>143238</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>178116</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>24,23%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>21,59%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>26,86%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>264</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>175009</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>158721</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>195439</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>25,03%</t>
-        </is>
-      </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>22,7%</t>
+          <t>21,67%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>27,95%</t>
+          <t>26,95%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2626,12 +2626,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>312500</t>
+          <t>311096</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>360328</t>
+          <t>361833</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2641,12 +2641,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>22,97%</t>
+          <t>22,87%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>26,49%</t>
+          <t>26,6%</t>
         </is>
       </c>
     </row>
@@ -2659,72 +2659,72 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>136</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>92135</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>78737</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>107798</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>13,18%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>11,26%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>15,42%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>119</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>78317</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>66446</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>93239</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>65561</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>92243</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
         <is>
           <t>11,85%</t>
         </is>
       </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>10,05%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>14,11%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>136</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>92135</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>78878</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>106461</t>
-        </is>
-      </c>
-      <c r="N21" s="2" t="inlineStr">
-        <is>
-          <t>13,18%</t>
-        </is>
-      </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>11,28%</t>
+          <t>9,92%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>15,22%</t>
+          <t>13,96%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2739,12 +2739,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>151377</t>
+          <t>151683</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>190237</t>
+          <t>190436</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2754,12 +2754,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>11,13%</t>
+          <t>11,15%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>13,98%</t>
+          <t>14,0%</t>
         </is>
       </c>
     </row>
@@ -2772,72 +2772,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>652</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>432150</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>410992</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>451184</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>61,8%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>58,77%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>64,52%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>629</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="K22" s="2" t="inlineStr">
         <is>
           <t>422489</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>403199</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>440745</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>402912</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>442704</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
         <is>
           <t>63,92%</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>61,0%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>66,68%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>652</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>432150</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>411008</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>452874</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>61,8%</t>
-        </is>
-      </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>58,77%</t>
+          <t>60,96%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>64,76%</t>
+          <t>66,98%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2852,12 +2852,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>824815</t>
+          <t>825590</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>881227</t>
+          <t>882480</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2867,12 +2867,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>60,64%</t>
+          <t>60,69%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>64,78%</t>
+          <t>64,87%</t>
         </is>
       </c>
     </row>
@@ -2885,57 +2885,57 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>1052</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>699294</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>699294</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>699294</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>989</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>660997</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="L23" s="2" t="inlineStr">
         <is>
           <t>660997</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
+      <c r="M23" s="2" t="inlineStr">
         <is>
           <t>660997</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>1052</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>699294</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>699294</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>699294</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -3055,7 +3055,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -3066,7 +3066,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -3234,72 +3234,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>41908</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>33574</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>52550</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>29,35%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>23,52%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>36,81%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>68</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>44492</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>35936</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>53370</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>36441</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>54295</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>31,25%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>25,24%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>37,48%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>41908</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>33240</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>51045</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>29,35%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>23,28%</t>
+          <t>25,59%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>35,75%</t>
+          <t>38,13%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>74430</t>
+          <t>73371</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>98171</t>
+          <t>98928</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3329,12 +3329,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>26,1%</t>
+          <t>25,73%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>34,43%</t>
+          <t>34,69%</t>
         </is>
       </c>
     </row>
@@ -3347,72 +3347,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>25208</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>17879</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>33846</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>17,66%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>12,52%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>23,71%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>29</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>18865</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>12844</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>26018</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>12547</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>26032</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>13,25%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>9,02%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>18,27%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>25208</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>18368</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>33419</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>17,66%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>12,87%</t>
+          <t>8,81%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>23,41%</t>
+          <t>18,28%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3427,12 +3427,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>34910</t>
+          <t>34768</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>55136</t>
+          <t>55131</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3442,12 +3442,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>12,24%</t>
+          <t>12,19%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>19,34%</t>
+          <t>19,33%</t>
         </is>
       </c>
     </row>
@@ -3460,72 +3460,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>106</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>75652</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>65384</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>85619</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>52,99%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>45,8%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>59,97%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>116</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>79032</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>69654</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>89232</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>68796</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>88116</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>55,5%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>48,92%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>62,67%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>106</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>75652</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>65388</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>84515</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>52,99%</t>
-        </is>
-      </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>45,8%</t>
+          <t>48,32%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>59,2%</t>
+          <t>61,88%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3540,12 +3540,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>140442</t>
+          <t>141919</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>167976</t>
+          <t>168496</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>49,25%</t>
+          <t>49,77%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>58,91%</t>
+          <t>59,09%</t>
         </is>
       </c>
     </row>
@@ -3573,57 +3573,57 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>203</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>142768</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>142768</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>142768</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>213</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>142390</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>142390</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
         <is>
           <t>142390</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>203</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>142768</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>142768</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>142768</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3690,72 +3690,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>118</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>85257</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>72878</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>97900</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>32,18%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>27,51%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>36,96%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>94</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>64665</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>54368</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>76135</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>54394</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>75860</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>27,52%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>23,14%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>32,4%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>118</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>85257</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>72939</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>98942</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>32,18%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>27,53%</t>
+          <t>23,15%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>37,35%</t>
+          <t>32,28%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3770,12 +3770,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>133831</t>
+          <t>133549</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>168574</t>
+          <t>167610</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3785,12 +3785,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>26,77%</t>
+          <t>26,71%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>33,72%</t>
+          <t>33,53%</t>
         </is>
       </c>
     </row>
@@ -3803,72 +3803,72 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>29502</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>21708</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>39385</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>11,14%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>8,19%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>14,87%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>37</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>26161</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>18616</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>34099</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>18950</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>34993</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
         <is>
           <t>11,13%</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>7,92%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>14,51%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>29502</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>22234</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>38988</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>11,14%</t>
-        </is>
-      </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>8,39%</t>
+          <t>8,06%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>14,72%</t>
+          <t>14,89%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -3883,12 +3883,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>45588</t>
+          <t>45335</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>67488</t>
+          <t>67551</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3898,12 +3898,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>9,12%</t>
+          <t>9,07%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>13,5%</t>
+          <t>13,51%</t>
         </is>
       </c>
     </row>
@@ -3916,72 +3916,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>208</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>150153</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>136767</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>163083</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>56,68%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>51,63%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>61,56%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>207</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>144167</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>132379</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>156794</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>131586</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>156542</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>61,35%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>56,33%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>66,72%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>208</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>150153</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>135190</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>162558</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>56,68%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>51,03%</t>
+          <t>56,0%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>61,36%</t>
+          <t>66,62%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3996,12 +3996,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>274573</t>
+          <t>275575</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>310913</t>
+          <t>313150</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4011,12 +4011,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>54,92%</t>
+          <t>55,13%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>62,19%</t>
+          <t>62,64%</t>
         </is>
       </c>
     </row>
@@ -4029,57 +4029,57 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>369</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>264912</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>264912</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>264912</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>338</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>234993</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
         <is>
           <t>234993</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>234993</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>369</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>264912</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>264912</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>264912</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4146,72 +4146,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>49138</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>39956</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>58698</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>31,73%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>25,8%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>37,9%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>67</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>47012</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>37742</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>56868</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>38372</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>57821</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>29,94%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>24,03%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>36,21%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>72</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>49138</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>39840</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>58417</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>31,73%</t>
-        </is>
-      </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>25,72%</t>
+          <t>24,43%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>37,72%</t>
+          <t>36,82%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4226,12 +4226,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>84065</t>
+          <t>84264</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>109660</t>
+          <t>110956</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4241,12 +4241,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>26,95%</t>
+          <t>27,01%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>35,16%</t>
+          <t>35,57%</t>
         </is>
       </c>
     </row>
@@ -4259,72 +4259,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>22258</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>15978</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>29948</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>14,37%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>10,32%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>19,34%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>24</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>16515</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>10446</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>23152</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>11411</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>24390</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>10,52%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>6,65%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>14,74%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>22258</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>15540</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>29719</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>14,37%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10,03%</t>
+          <t>7,27%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>19,19%</t>
+          <t>15,53%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4339,12 +4339,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>29544</t>
+          <t>29670</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>48228</t>
+          <t>48395</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4354,12 +4354,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>9,47%</t>
+          <t>9,51%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>15,46%</t>
+          <t>15,51%</t>
         </is>
       </c>
     </row>
@@ -4372,72 +4372,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>119</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>83488</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>73679</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>94741</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>53,9%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>47,57%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>61,17%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>132</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>93516</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>83920</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>103466</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>82186</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>103119</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>59,55%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>53,44%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>65,88%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>119</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>83488</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>73336</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>94418</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>53,9%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>47,35%</t>
+          <t>52,33%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>60,96%</t>
+          <t>65,66%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4452,12 +4452,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>162867</t>
+          <t>162186</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>190946</t>
+          <t>190883</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>52,21%</t>
+          <t>51,99%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>61,21%</t>
+          <t>61,19%</t>
         </is>
       </c>
     </row>
@@ -4490,52 +4490,52 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
+          <t>154884</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>154884</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>154884</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>223</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
           <t>157043</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>157043</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>157043</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>223</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>154884</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>154884</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>154884</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4602,72 +4602,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>57508</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>48075</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>66822</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>32,57%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>27,22%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>37,84%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>65</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>45386</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>36424</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>55495</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>36200</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>55328</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>27,03%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>21,69%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>33,05%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>85</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>57508</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>48102</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>68364</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>32,57%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>27,24%</t>
+          <t>21,56%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>38,71%</t>
+          <t>32,95%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4682,12 +4682,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>89717</t>
+          <t>90224</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>118299</t>
+          <t>118582</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>26,04%</t>
+          <t>26,19%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>34,34%</t>
+          <t>34,42%</t>
         </is>
       </c>
     </row>
@@ -4715,72 +4715,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>14552</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>9499</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>21165</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>8,24%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>5,38%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>11,99%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>27</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>19483</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>13380</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>26596</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>12663</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>26848</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>11,6%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>7,97%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>15,84%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>14552</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>9241</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>21488</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>8,24%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>7,54%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>12,17%</t>
+          <t>15,99%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4795,12 +4795,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>26477</t>
+          <t>26053</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>44154</t>
+          <t>44514</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>7,69%</t>
+          <t>7,56%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>12,82%</t>
+          <t>12,92%</t>
         </is>
       </c>
     </row>
@@ -4828,72 +4828,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>153</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>104526</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>94307</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>114705</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>59,19%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>53,41%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>64,96%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>146</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>103060</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>93091</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>113713</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>92902</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>113784</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>61,37%</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>55,43%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>67,71%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>153</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>104526</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>93457</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>115069</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>59,19%</t>
-        </is>
-      </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>52,92%</t>
+          <t>55,32%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>65,16%</t>
+          <t>67,76%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -4908,12 +4908,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>193643</t>
+          <t>190815</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>224043</t>
+          <t>221850</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>56,21%</t>
+          <t>55,39%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>65,03%</t>
+          <t>64,39%</t>
         </is>
       </c>
     </row>
@@ -4941,57 +4941,57 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>260</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>176586</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>176586</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>176586</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>238</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>167929</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
         <is>
           <t>167929</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="M19" s="2" t="inlineStr">
         <is>
           <t>167929</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>260</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>176586</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>176586</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>176586</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5058,72 +5058,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>337</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>233811</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>212975</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>256717</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>31,63%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>28,81%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>34,73%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>294</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>201554</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>183510</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>222753</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>182794</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>222607</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>28,7%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>26,13%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>31,72%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>337</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>233811</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>214237</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>253551</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>31,63%</t>
-        </is>
-      </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>28,98%</t>
+          <t>26,03%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>34,3%</t>
+          <t>31,69%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5138,12 +5138,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>409343</t>
+          <t>407334</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>464516</t>
+          <t>465189</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>28,4%</t>
+          <t>28,26%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>32,22%</t>
+          <t>32,27%</t>
         </is>
       </c>
     </row>
@@ -5171,72 +5171,72 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>132</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>91520</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>77898</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>107546</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>12,38%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>10,54%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>14,55%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>117</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>81025</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>68087</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>95181</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>68415</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>95817</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
         <is>
           <t>11,54%</t>
         </is>
       </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>9,69%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>13,55%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>132</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>91520</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>78072</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>106403</t>
-        </is>
-      </c>
-      <c r="N21" s="2" t="inlineStr">
-        <is>
-          <t>12,38%</t>
-        </is>
-      </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>10,56%</t>
+          <t>9,74%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>14,4%</t>
+          <t>13,64%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -5251,12 +5251,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>155473</t>
+          <t>154856</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>194805</t>
+          <t>194797</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -5266,7 +5266,7 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>10,79%</t>
+          <t>10,74%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
@@ -5284,72 +5284,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>586</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>413819</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>391634</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>436403</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>55,99%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>52,98%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>59,04%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>601</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="K22" s="2" t="inlineStr">
         <is>
           <t>419776</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>398049</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>441660</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>395958</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>440843</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
         <is>
           <t>59,77%</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>56,67%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>62,88%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>586</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>413819</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>393101</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>436109</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>55,99%</t>
-        </is>
-      </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>53,18%</t>
+          <t>56,38%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>59,0%</t>
+          <t>62,77%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5364,12 +5364,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>802786</t>
+          <t>802322</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>865015</t>
+          <t>864530</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5379,12 +5379,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>55,69%</t>
+          <t>55,66%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>60,01%</t>
+          <t>59,97%</t>
         </is>
       </c>
     </row>
@@ -5397,57 +5397,57 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>1055</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>739150</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>739150</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>739150</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>1012</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>702355</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="L23" s="2" t="inlineStr">
         <is>
           <t>702355</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
+      <c r="M23" s="2" t="inlineStr">
         <is>
           <t>702355</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>1055</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>739150</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>739150</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>739150</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5567,7 +5567,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -5578,7 +5578,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -5746,72 +5746,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>26170</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>19369</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>33664</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>22,05%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>16,32%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>28,36%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>29</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>17070</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>11844</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>23544</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>12066</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>23538</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>13,35%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>9,26%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>18,42%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>26170</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>19570</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>33817</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>22,05%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>16,49%</t>
+          <t>9,44%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>28,49%</t>
+          <t>18,41%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5826,12 +5826,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>34346</t>
+          <t>34565</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>54477</t>
+          <t>54052</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5841,12 +5841,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>13,93%</t>
+          <t>14,02%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>22,1%</t>
+          <t>21,92%</t>
         </is>
       </c>
     </row>
@@ -5859,72 +5859,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>24179</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>17374</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>32278</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>20,37%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>14,64%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>27,19%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>30</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>18151</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>12615</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>25198</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>12874</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>24588</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>14,2%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>9,87%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>19,71%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>24179</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>17415</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>32233</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>20,37%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>14,67%</t>
+          <t>10,07%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>27,15%</t>
+          <t>19,23%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5939,12 +5939,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>34201</t>
+          <t>31974</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>52643</t>
+          <t>51365</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5954,12 +5954,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>13,87%</t>
+          <t>12,97%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>21,35%</t>
+          <t>20,83%</t>
         </is>
       </c>
     </row>
@@ -5972,72 +5972,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>105</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>68362</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>59895</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>76884</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>57,59%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>50,45%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>64,77%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>146</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>92626</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>83788</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>99835</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>84413</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>99881</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>72,45%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>65,54%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>78,09%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>105</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>68362</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>59584</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>77330</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>57,59%</t>
-        </is>
-      </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>50,19%</t>
+          <t>66,03%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>65,14%</t>
+          <t>78,13%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6052,12 +6052,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>149046</t>
+          <t>147218</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>172830</t>
+          <t>171837</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6067,12 +6067,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>60,45%</t>
+          <t>59,71%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>70,1%</t>
+          <t>69,69%</t>
         </is>
       </c>
     </row>
@@ -6085,57 +6085,57 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>179</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>118711</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>118711</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>118711</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>205</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>127847</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>127847</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
         <is>
           <t>127847</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>179</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>118711</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>118711</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>118711</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6202,72 +6202,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>41988</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>33506</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>52269</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>16,48%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>13,15%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>20,52%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>56</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>36001</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>27917</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>45208</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>27599</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>45150</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>17,25%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>13,37%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>21,66%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>41988</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>33380</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>51542</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>16,48%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>13,1%</t>
+          <t>13,22%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>20,24%</t>
+          <t>21,63%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6282,12 +6282,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>65567</t>
+          <t>66455</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>91473</t>
+          <t>92013</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>14,15%</t>
+          <t>14,34%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>19,74%</t>
+          <t>19,85%</t>
         </is>
       </c>
     </row>
@@ -6315,72 +6315,72 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>43077</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>34112</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>53287</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>16,91%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>13,39%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>20,92%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>51</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>31513</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>24316</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>40517</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>24507</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>41154</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
         <is>
           <t>15,1%</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>11,65%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>19,41%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>43077</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>34836</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>54189</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>16,91%</t>
-        </is>
-      </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>13,68%</t>
+          <t>11,74%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>21,27%</t>
+          <t>19,72%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -6395,12 +6395,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>62148</t>
+          <t>62966</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>87271</t>
+          <t>87875</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6410,12 +6410,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>13,41%</t>
+          <t>13,59%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>18,83%</t>
+          <t>18,96%</t>
         </is>
       </c>
     </row>
@@ -6428,72 +6428,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>245</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>169646</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>156534</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>180929</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>66,6%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>61,46%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>71,03%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>222</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>141220</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>130572</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>150727</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>130162</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>151773</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>67,66%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>62,55%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>72,21%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>245</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>169646</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>156494</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>181837</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>66,6%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>61,44%</t>
+          <t>62,36%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>71,39%</t>
+          <t>72,71%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6508,12 +6508,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>295938</t>
+          <t>295365</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>326384</t>
+          <t>326822</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6523,12 +6523,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>63,86%</t>
+          <t>63,73%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>70,43%</t>
+          <t>70,52%</t>
         </is>
       </c>
     </row>
@@ -6541,57 +6541,57 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>375</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>254711</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>254711</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>254711</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>329</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>208734</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
         <is>
           <t>208734</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>208734</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>375</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>254711</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>254711</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>254711</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6658,72 +6658,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>35483</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>27524</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>46652</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>19,17%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>14,87%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>25,2%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>57</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>38970</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>30516</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>48035</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>30005</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>48868</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>20,82%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>16,31%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>25,67%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>35483</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>26822</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>45440</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>19,17%</t>
-        </is>
-      </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>14,49%</t>
+          <t>16,03%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>24,55%</t>
+          <t>26,11%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6738,12 +6738,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>62714</t>
+          <t>63085</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>88571</t>
+          <t>88025</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6753,12 +6753,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>16,85%</t>
+          <t>16,95%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>23,79%</t>
+          <t>23,65%</t>
         </is>
       </c>
     </row>
@@ -6771,72 +6771,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>21423</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>14913</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>29083</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>11,57%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>8,06%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>15,71%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>53</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>37471</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>29382</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>47327</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>28660</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>48376</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>20,02%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>15,7%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>25,29%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>21423</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>15525</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>29468</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>11,57%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>8,39%</t>
+          <t>15,31%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>15,92%</t>
+          <t>25,85%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6851,12 +6851,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>47496</t>
+          <t>47473</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>70468</t>
+          <t>70778</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6866,12 +6866,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>12,76%</t>
+          <t>12,75%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>18,93%</t>
+          <t>19,01%</t>
         </is>
       </c>
     </row>
@@ -6884,72 +6884,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>178</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>128215</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>117790</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>138282</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>69,26%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>63,63%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>74,7%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>159</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>110712</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>100051</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>120757</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>99083</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>121671</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>59,16%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>53,46%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>64,52%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>178</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>128215</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>116538</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>138452</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>69,26%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>62,95%</t>
+          <t>52,94%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>74,79%</t>
+          <t>65,01%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6964,12 +6964,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>223814</t>
+          <t>223872</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>254546</t>
+          <t>253101</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6979,12 +6979,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>60,12%</t>
+          <t>60,14%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>68,38%</t>
+          <t>67,99%</t>
         </is>
       </c>
     </row>
@@ -6997,57 +6997,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>258</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>185120</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>185120</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>185120</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>269</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>187153</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>187153</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>187153</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>258</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>185120</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>185120</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>185120</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7114,72 +7114,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>34706</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>26545</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>43448</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>20,96%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>16,03%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>26,24%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>65</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>45822</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>37114</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>56720</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>35865</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>55811</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>27,7%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>22,44%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>34,29%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>34706</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>26925</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>44009</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>20,96%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>16,26%</t>
+          <t>21,68%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>26,58%</t>
+          <t>33,74%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7194,12 +7194,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>67153</t>
+          <t>66888</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>93968</t>
+          <t>93472</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7209,12 +7209,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>20,29%</t>
+          <t>20,21%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>28,39%</t>
+          <t>28,24%</t>
         </is>
       </c>
     </row>
@@ -7227,72 +7227,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>27070</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>19489</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>35806</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>16,35%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>11,77%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>21,63%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>28</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>20412</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>13566</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>27745</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>14260</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>28460</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>12,34%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>8,2%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>16,78%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>27070</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>20119</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>35741</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>16,35%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>12,15%</t>
+          <t>8,62%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>21,59%</t>
+          <t>17,21%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7307,12 +7307,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>37054</t>
+          <t>37847</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>58494</t>
+          <t>59180</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7322,12 +7322,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>11,2%</t>
+          <t>11,44%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>17,67%</t>
+          <t>17,88%</t>
         </is>
       </c>
     </row>
@@ -7340,72 +7340,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>139</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>103774</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>93150</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>113826</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>62,68%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>56,27%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>68,76%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>142</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>99161</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>87740</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>108942</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>89059</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>110681</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>59,95%</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>53,05%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>65,87%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>139</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>103774</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>92867</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>113231</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>62,68%</t>
-        </is>
-      </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>56,1%</t>
+          <t>53,85%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>68,4%</t>
+          <t>66,92%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -7420,12 +7420,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>188708</t>
+          <t>187525</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>217946</t>
+          <t>218345</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -7435,12 +7435,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>57,02%</t>
+          <t>56,66%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>65,86%</t>
+          <t>65,98%</t>
         </is>
       </c>
     </row>
@@ -7453,57 +7453,57 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>223</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>165550</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>165550</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>165550</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>235</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>165395</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
         <is>
           <t>165395</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="M19" s="2" t="inlineStr">
         <is>
           <t>165395</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>223</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>165550</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>165550</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>165550</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7570,72 +7570,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>138348</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>121697</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>154568</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>19,11%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>16,81%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>21,35%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>207</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>137863</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>121123</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>155373</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>122026</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>154970</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>20,01%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>17,58%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>22,55%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>138348</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>121841</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>155888</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>19,11%</t>
-        </is>
-      </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>16,83%</t>
+          <t>17,71%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>21,53%</t>
+          <t>22,49%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7650,12 +7650,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>254897</t>
+          <t>253057</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>300948</t>
+          <t>299968</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7665,12 +7665,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>18,04%</t>
+          <t>17,91%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>21,3%</t>
+          <t>21,23%</t>
         </is>
       </c>
     </row>
@@ -7683,72 +7683,72 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>168</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>115748</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>101726</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>132174</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>15,99%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>14,05%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>18,25%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>162</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>107548</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>92687</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>124248</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>94122</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>125240</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
         <is>
           <t>15,61%</t>
         </is>
       </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>13,45%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>18,03%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>168</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>115748</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>99988</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>132961</t>
-        </is>
-      </c>
-      <c r="N21" s="2" t="inlineStr">
-        <is>
-          <t>15,99%</t>
-        </is>
-      </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>13,81%</t>
+          <t>13,66%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>18,36%</t>
+          <t>18,17%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -7763,12 +7763,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>202845</t>
+          <t>203689</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>244968</t>
+          <t>245852</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -7778,12 +7778,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>14,35%</t>
+          <t>14,41%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>17,33%</t>
+          <t>17,4%</t>
         </is>
       </c>
     </row>
@@ -7796,72 +7796,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>667</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>469996</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>448422</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>489988</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>64,91%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>61,93%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>67,67%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>669</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="K22" s="2" t="inlineStr">
         <is>
           <t>443719</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>423121</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>463199</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>421422</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>461865</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
         <is>
           <t>64,39%</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>61,4%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>67,21%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>667</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>469996</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>451236</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>490771</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>64,91%</t>
-        </is>
-      </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>62,32%</t>
+          <t>61,15%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>67,78%</t>
+          <t>67,02%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7876,12 +7876,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>886026</t>
+          <t>887016</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>944300</t>
+          <t>944614</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7891,12 +7891,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>62,7%</t>
+          <t>62,77%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>66,82%</t>
+          <t>66,84%</t>
         </is>
       </c>
     </row>
@@ -7909,57 +7909,57 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>1035</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>724092</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>724092</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>724092</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>1038</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>689130</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="L23" s="2" t="inlineStr">
         <is>
           <t>689130</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
+      <c r="M23" s="2" t="inlineStr">
         <is>
           <t>689130</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>1035</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>724092</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>724092</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>724092</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
